--- a/rawData/Bais/Bais2015Data/BaisExtract.xlsx
+++ b/rawData/Bais/Bais2015Data/BaisExtract.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/valade/EcoSols_Nextcloud/Substitution/Substitution_AV/manuscript/biblio/Bais/Bais2015Data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/valade/Documents/GitHub/Wood-Carbon/rawData/Bais/Bais2015Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6F59BBD-78F2-9746-8E86-B6D9093F9F90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FAF5803-5011-5A4D-95F2-67E84B3E1AE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-36520" yWindow="-11400" windowWidth="21820" windowHeight="14260" activeTab="4" xr2:uid="{FC68D7D9-CD40-674D-8DDE-EDB023EC591D}"/>
   </bookViews>
@@ -2822,9 +2822,6 @@
     <t>levelFig3a</t>
   </si>
   <si>
-    <t>Country</t>
-  </si>
-  <si>
     <t>Alpha-2 code</t>
   </si>
   <si>
@@ -3120,6 +3117,9 @@
   </si>
   <si>
     <t>Åland Islands</t>
+  </si>
+  <si>
+    <t>country</t>
   </si>
 </sst>
 </file>
@@ -16244,16 +16244,16 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" s="5" t="s">
+        <v>1024</v>
+      </c>
+      <c r="B1" s="5" t="s">
         <v>925</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="C1" s="5" t="s">
         <v>926</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="D1" s="5" t="s">
         <v>927</v>
-      </c>
-      <c r="D1" s="5" t="s">
-        <v>928</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.2">
@@ -16370,7 +16370,7 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="B10" t="s">
         <v>461</v>
@@ -16468,7 +16468,7 @@
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="B17" t="s">
         <v>146</v>
@@ -16608,7 +16608,7 @@
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="B27" t="s">
         <v>732</v>
@@ -16622,13 +16622,13 @@
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
+        <v>931</v>
+      </c>
+      <c r="B28" t="s">
         <v>932</v>
       </c>
-      <c r="B28" t="s">
+      <c r="C28" t="s">
         <v>933</v>
-      </c>
-      <c r="C28" t="s">
-        <v>934</v>
       </c>
       <c r="D28">
         <v>535</v>
@@ -16636,7 +16636,7 @@
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="B29" t="s">
         <v>201</v>
@@ -16664,13 +16664,13 @@
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
+        <v>935</v>
+      </c>
+      <c r="B31" t="s">
         <v>936</v>
       </c>
-      <c r="B31" t="s">
+      <c r="C31" t="s">
         <v>937</v>
-      </c>
-      <c r="C31" t="s">
-        <v>938</v>
       </c>
       <c r="D31">
         <v>74</v>
@@ -16692,7 +16692,7 @@
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="B33" t="s">
         <v>173</v>
@@ -16706,7 +16706,7 @@
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="B34" t="s">
         <v>315</v>
@@ -16818,7 +16818,7 @@
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="B42" t="s">
         <v>674</v>
@@ -16832,7 +16832,7 @@
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="B43" t="s">
         <v>287</v>
@@ -16888,13 +16888,13 @@
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
+        <v>942</v>
+      </c>
+      <c r="B47" t="s">
         <v>943</v>
       </c>
-      <c r="B47" t="s">
+      <c r="C47" t="s">
         <v>944</v>
-      </c>
-      <c r="C47" t="s">
-        <v>945</v>
       </c>
       <c r="D47">
         <v>162</v>
@@ -16902,13 +16902,13 @@
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
+        <v>945</v>
+      </c>
+      <c r="B48" t="s">
         <v>946</v>
       </c>
-      <c r="B48" t="s">
+      <c r="C48" t="s">
         <v>947</v>
-      </c>
-      <c r="C48" t="s">
-        <v>948</v>
       </c>
       <c r="D48">
         <v>166</v>
@@ -16930,7 +16930,7 @@
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="B50" t="s">
         <v>684</v>
@@ -16944,7 +16944,7 @@
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="B51" t="s">
         <v>218</v>
@@ -16958,7 +16958,7 @@
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="B52" t="s">
         <v>220</v>
@@ -16972,7 +16972,7 @@
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="B53" t="s">
         <v>179</v>
@@ -17126,7 +17126,7 @@
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="B64" t="s">
         <v>329</v>
@@ -17182,7 +17182,7 @@
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="B68" t="s">
         <v>483</v>
@@ -17224,7 +17224,7 @@
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="B71" t="s">
         <v>376</v>
@@ -17252,7 +17252,7 @@
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="B73" t="s">
         <v>715</v>
@@ -17266,7 +17266,7 @@
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="B74" t="s">
         <v>170</v>
@@ -17322,13 +17322,13 @@
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
+        <v>957</v>
+      </c>
+      <c r="B78" t="s">
         <v>958</v>
       </c>
-      <c r="B78" t="s">
+      <c r="C78" t="s">
         <v>959</v>
-      </c>
-      <c r="C78" t="s">
-        <v>960</v>
       </c>
       <c r="D78">
         <v>254</v>
@@ -17336,7 +17336,7 @@
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
       <c r="B79" t="s">
         <v>104</v>
@@ -17350,7 +17350,7 @@
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
       <c r="B80" t="s">
         <v>108</v>
@@ -17378,7 +17378,7 @@
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
       <c r="B82" t="s">
         <v>15</v>
@@ -17490,13 +17490,13 @@
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
+        <v>963</v>
+      </c>
+      <c r="B90" t="s">
         <v>964</v>
       </c>
-      <c r="B90" t="s">
+      <c r="C90" t="s">
         <v>965</v>
-      </c>
-      <c r="C90" t="s">
-        <v>966</v>
       </c>
       <c r="D90">
         <v>312</v>
@@ -17602,7 +17602,7 @@
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="B98" t="s">
         <v>678</v>
@@ -17616,13 +17616,13 @@
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
+        <v>967</v>
+      </c>
+      <c r="B99" t="s">
         <v>968</v>
       </c>
-      <c r="B99" t="s">
+      <c r="C99" t="s">
         <v>969</v>
-      </c>
-      <c r="C99" t="s">
-        <v>970</v>
       </c>
       <c r="D99">
         <v>336</v>
@@ -17714,7 +17714,7 @@
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A106" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="B106" t="s">
         <v>404</v>
@@ -17896,7 +17896,7 @@
     </row>
     <row r="119" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A119" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="B119" t="s">
         <v>623</v>
@@ -17910,7 +17910,7 @@
     </row>
     <row r="120" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A120" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
       <c r="B120" t="s">
         <v>117</v>
@@ -17952,7 +17952,7 @@
     </row>
     <row r="123" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A123" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
       <c r="B123" t="s">
         <v>759</v>
@@ -18176,7 +18176,7 @@
     </row>
     <row r="139" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A139" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="B139" t="s">
         <v>119</v>
@@ -18190,13 +18190,13 @@
     </row>
     <row r="140" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A140" t="s">
+        <v>975</v>
+      </c>
+      <c r="B140" t="s">
         <v>976</v>
       </c>
-      <c r="B140" t="s">
+      <c r="C140" t="s">
         <v>977</v>
-      </c>
-      <c r="C140" t="s">
-        <v>978</v>
       </c>
       <c r="D140">
         <v>474</v>
@@ -18232,13 +18232,13 @@
     </row>
     <row r="143" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A143" t="s">
+        <v>978</v>
+      </c>
+      <c r="B143" t="s">
         <v>979</v>
       </c>
-      <c r="B143" t="s">
+      <c r="C143" t="s">
         <v>980</v>
-      </c>
-      <c r="C143" t="s">
-        <v>981</v>
       </c>
       <c r="D143">
         <v>175</v>
@@ -18260,7 +18260,7 @@
     </row>
     <row r="145" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A145" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="B145" t="s">
         <v>189</v>
@@ -18274,7 +18274,7 @@
     </row>
     <row r="146" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A146" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
       <c r="B146" t="s">
         <v>397</v>
@@ -18428,7 +18428,7 @@
     </row>
     <row r="157" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A157" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="B157" t="s">
         <v>17</v>
@@ -18484,7 +18484,7 @@
     </row>
     <row r="161" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A161" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="B161" t="s">
         <v>719</v>
@@ -18540,7 +18540,7 @@
     </row>
     <row r="165" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A165" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="B165" t="s">
         <v>558</v>
@@ -18610,7 +18610,7 @@
     </row>
     <row r="170" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A170" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="B170" t="s">
         <v>205</v>
@@ -18680,7 +18680,7 @@
     </row>
     <row r="175" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A175" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="B175" t="s">
         <v>70</v>
@@ -18694,7 +18694,7 @@
     </row>
     <row r="176" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A176" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
       <c r="B176" t="s">
         <v>100</v>
@@ -18764,7 +18764,7 @@
     </row>
     <row r="181" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A181" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="B181" t="s">
         <v>256</v>
@@ -18792,7 +18792,7 @@
     </row>
     <row r="183" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A183" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="B183" t="s">
         <v>20</v>
@@ -18820,13 +18820,13 @@
     </row>
     <row r="185" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A185" t="s">
+        <v>991</v>
+      </c>
+      <c r="B185" t="s">
         <v>992</v>
       </c>
-      <c r="B185" t="s">
+      <c r="C185" t="s">
         <v>993</v>
-      </c>
-      <c r="C185" t="s">
-        <v>994</v>
       </c>
       <c r="D185">
         <v>638</v>
@@ -18834,7 +18834,7 @@
     </row>
     <row r="186" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A186" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="B186" t="s">
         <v>666</v>
@@ -18848,7 +18848,7 @@
     </row>
     <row r="187" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A187" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
       <c r="B187" t="s">
         <v>681</v>
@@ -18862,7 +18862,7 @@
     </row>
     <row r="188" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A188" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="B188" t="s">
         <v>547</v>
@@ -18890,7 +18890,7 @@
     </row>
     <row r="190" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A190" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="B190" t="s">
         <v>747</v>
@@ -18904,7 +18904,7 @@
     </row>
     <row r="191" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A191" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="B191" t="s">
         <v>68</v>
@@ -18918,7 +18918,7 @@
     </row>
     <row r="192" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A192" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
       <c r="B192" t="s">
         <v>534</v>
@@ -18960,7 +18960,7 @@
     </row>
     <row r="195" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A195" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
       <c r="B195" t="s">
         <v>539</v>
@@ -19058,7 +19058,7 @@
     </row>
     <row r="202" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A202" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="B202" t="s">
         <v>713</v>
@@ -19100,7 +19100,7 @@
     </row>
     <row r="205" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A205" t="s">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="B205" t="s">
         <v>661</v>
@@ -19142,7 +19142,7 @@
     </row>
     <row r="208" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A208" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="B208" t="s">
         <v>711</v>
@@ -19156,7 +19156,7 @@
     </row>
     <row r="209" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A209" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="B209" t="s">
         <v>417</v>
@@ -19198,7 +19198,7 @@
     </row>
     <row r="212" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A212" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="B212" t="s">
         <v>291</v>
@@ -19226,13 +19226,13 @@
     </row>
     <row r="214" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A214" t="s">
+        <v>1006</v>
+      </c>
+      <c r="B214" t="s">
         <v>1007</v>
       </c>
-      <c r="B214" t="s">
+      <c r="C214" t="s">
         <v>1008</v>
-      </c>
-      <c r="C214" t="s">
-        <v>1009</v>
       </c>
       <c r="D214">
         <v>744</v>
@@ -19268,7 +19268,7 @@
     </row>
     <row r="217" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A217" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="B217" t="s">
         <v>238</v>
@@ -19282,7 +19282,7 @@
     </row>
     <row r="218" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A218" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="B218" t="s">
         <v>657</v>
@@ -19310,7 +19310,7 @@
     </row>
     <row r="220" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A220" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
       <c r="B220" t="s">
         <v>407</v>
@@ -19366,13 +19366,13 @@
     </row>
     <row r="224" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A224" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="B224" t="s">
         <v>76</v>
       </c>
       <c r="C224" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="D224">
         <v>772</v>
@@ -19450,7 +19450,7 @@
     </row>
     <row r="230" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A230" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="B230" t="s">
         <v>74</v>
@@ -19506,7 +19506,7 @@
     </row>
     <row r="234" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A234" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
       <c r="B234" t="s">
         <v>241</v>
@@ -19534,7 +19534,7 @@
     </row>
     <row r="236" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A236" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="B236" t="s">
         <v>136</v>
@@ -19604,7 +19604,7 @@
     </row>
     <row r="241" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A241" t="s">
-        <v>1018</v>
+        <v>1017</v>
       </c>
       <c r="B241" t="s">
         <v>126</v>
@@ -19618,7 +19618,7 @@
     </row>
     <row r="242" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A242" t="s">
-        <v>1019</v>
+        <v>1018</v>
       </c>
       <c r="B242" t="s">
         <v>35</v>
@@ -19632,7 +19632,7 @@
     </row>
     <row r="243" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A243" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="B243" t="s">
         <v>139</v>
@@ -19646,7 +19646,7 @@
     </row>
     <row r="244" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A244" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="B244" t="s">
         <v>141</v>
@@ -19660,7 +19660,7 @@
     </row>
     <row r="245" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A245" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="B245" t="s">
         <v>701</v>
@@ -19674,7 +19674,7 @@
     </row>
     <row r="246" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A246" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="B246" t="s">
         <v>801</v>
@@ -19730,7 +19730,7 @@
     </row>
     <row r="250" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A250" t="s">
-        <v>1024</v>
+        <v>1023</v>
       </c>
       <c r="B250" t="s">
         <v>167</v>
